--- a/output/pdf_financials_xlsx/MAX.xlsx
+++ b/output/pdf_financials_xlsx/MAX.xlsx
@@ -6609,52 +6609,52 @@
         <v>1.393485</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.458599</v>
+        <v>1.393485</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.881765</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.997335</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.997335</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.125781</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.133423</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.133423</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.133423</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.133423</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.738416</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.876054</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.363804</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.259075</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>7.259075</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>8.087647</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>7.799323</v>
       </c>
     </row>
     <row r="93">
@@ -8298,16 +8298,16 @@
         <v>0</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-6.254891</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>4.125936</v>
+        <v>-1.480744</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-1.14556</v>
       </c>
       <c r="T118" s="3" t="n">
-        <v>0</v>
+        <v>-2.55403</v>
       </c>
     </row>
     <row r="119">
@@ -9906,7 +9906,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -11105,7 +11109,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11971,7 +11979,11 @@
           <t>Prepaids and deposits 13</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13200,7 +13212,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -15339,7 +15355,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -17144,7 +17164,11 @@
           <t>Share-based payment reserve 7,8</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -17998,7 +18022,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -18210,7 +18238,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -18985,7 +19017,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -19960,7 +19996,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -21389,7 +21429,11 @@
           <t>Share based payment reserve 11</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21944,7 +21988,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -23282,7 +23330,11 @@
           <t>Share-based payment reserve 11 1,881,765</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -27541,7 +27593,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -27646,7 +27702,11 @@
           <t>Advances received from exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -29832,7 +29892,11 @@
           <t>Advances received from exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -33362,7 +33426,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MAX.xlsx
+++ b/output/pdf_financials_xlsx/MAX.xlsx
@@ -1089,25 +1089,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.22229</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.27389</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.09547</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023856</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.015828</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011805</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002196</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1125,25 +1125,25 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003145</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.006354</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.290451</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.460542</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.153452</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>0.006135</v>
       </c>
     </row>
     <row r="13">
@@ -2135,25 +2135,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.093554</v>
+        <v>-1.315844</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.412762</v>
+        <v>-1.686652</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.660805</v>
+        <v>-4.756275</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.502315</v>
+        <v>-0.5261710000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.112646</v>
+        <v>-1.128474</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.840099</v>
+        <v>-1.851904</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.094521</v>
+        <v>-1.096717</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.245936</v>
@@ -2171,25 +2171,25 @@
         <v>-3.468206</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.780842</v>
+        <v>-4.783987</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.206965</v>
+        <v>-5.207008</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.075878</v>
+        <v>-5.082232</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.652234</v>
+        <v>-5.942685</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-7.577368</v>
+        <v>-8.03791</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-5.674833</v>
+        <v>-5.828285</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>-3.297555</v>
+        <v>-3.30369</v>
       </c>
     </row>
     <row r="28">
@@ -2263,25 +2263,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.093554</v>
+        <v>-1.315844</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.412762</v>
+        <v>-1.686652</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.660805</v>
+        <v>-4.756275</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.502315</v>
+        <v>-0.5261710000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.112646</v>
+        <v>-1.128474</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.840099</v>
+        <v>-1.851904</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.094521</v>
+        <v>-1.096717</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.245936</v>
@@ -2299,25 +2299,25 @@
         <v>-3.468206</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.775139</v>
+        <v>-4.778284</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.196913</v>
+        <v>-5.196956</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.056278</v>
+        <v>-5.062632</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.605356</v>
+        <v>-5.895807</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-7.45671</v>
+        <v>-7.917252</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-5.546696</v>
+        <v>-5.700148</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-3.09595</v>
+        <v>-3.102085</v>
       </c>
     </row>
     <row r="30">
@@ -2625,13 +2625,13 @@
         <v>0.203229</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002903</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.088575</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.043306</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.228825</v>
@@ -2757,13 +2757,13 @@
         <v>0.203229</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002903</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.088575</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.043306</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.228825</v>
@@ -3549,13 +3549,13 @@
         <v>0.004351</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.007818</v>
+        <v>0.004915</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.093678</v>
+        <v>0.005103</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.044302</v>
+        <v>0.0009959999999999999</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.005333</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -20107,7 +20107,11 @@
           <t>Reclamation deposits 4, 9</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20331,7 +20335,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -20882,7 +20890,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -22660,7 +22672,11 @@
           <t>Reclamation deposits 7 68,183</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -52353,7 +52369,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -61193,7 +61209,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -66677,7 +66693,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -67121,7 +67137,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -69858,7 +69874,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -76377,7 +76393,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E610" s="5" t="n">

--- a/output/pdf_financials_xlsx/MAX.xlsx
+++ b/output/pdf_financials_xlsx/MAX.xlsx
@@ -4688,25 +4688,25 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.635754</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.694841</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.386139</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>1.407188</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.9309460000000001</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>2.105563</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>0</v>
+        <v>0.930273</v>
       </c>
     </row>
     <row r="65">
@@ -4952,25 +4952,25 @@
         <v>0.384334</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.678254</v>
+        <v>1.314008</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.734841</v>
+        <v>1.429682</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.487824</v>
+        <v>0.873963</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>1.627671</v>
+        <v>3.034859</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>1.208438</v>
+        <v>2.139384</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>3.435848</v>
+        <v>5.541411</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>1.38082</v>
+        <v>2.311093</v>
       </c>
     </row>
     <row r="69">
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.038583</v>
       </c>
       <c r="S110" s="3" t="n">
         <v>0</v>
@@ -7811,7 +7811,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005148</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7841,25 +7841,25 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.027375</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.087189</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.056984</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.285016</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.06113</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.41997</v>
       </c>
       <c r="T111" s="3" t="n">
-        <v>0</v>
+        <v>-0.028658</v>
       </c>
     </row>
     <row r="112">
@@ -8073,10 +8073,10 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.066973</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005148</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -9351,25 +9351,25 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.027375</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.087189</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.056984</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.285016</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.06113</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.41997</v>
       </c>
       <c r="T134" s="3" t="n">
-        <v>0</v>
+        <v>-0.028658</v>
       </c>
     </row>
     <row r="135">
@@ -9385,7 +9385,7 @@
         <v>-0.369717</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.6205079999999999</v>
+        <v>-0.625656</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.498284</v>
@@ -9415,25 +9415,25 @@
         <v>-3.45017</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-3.708371</v>
+        <v>-3.735746</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-3.441751</v>
+        <v>-3.52894</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-4.438058</v>
+        <v>-4.495042</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-3.572008</v>
+        <v>-3.857024</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-3.524917</v>
+        <v>-3.586047</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-2.624969</v>
+        <v>-3.044939</v>
       </c>
       <c r="T135" s="3" t="n">
-        <v>-3.398338</v>
+        <v>-3.426996</v>
       </c>
     </row>
   </sheetData>
@@ -27831,7 +27831,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -29462,7 +29466,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -30023,7 +30031,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -33668,7 +33680,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -35192,7 +35208,11 @@
           <t>Advances on private placement</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -37265,7 +37285,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -37376,7 +37400,11 @@
           <t>Advances on private placement</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -38809,7 +38837,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -46586,7 +46618,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -49012,7 +49048,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -49448,7 +49488,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -76718,7 +76762,11 @@
           <t>Future income tax recovery (Note 8)</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E613" t="inlineStr">
         <is>
           <t>-</t>
@@ -78129,7 +78177,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
